--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,26 +448,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>122675151.49</v>
+        <v>86596208.19000001</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>36078943.3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -477,16 +477,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>36078943.3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -505,7 +505,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -524,26 +524,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86596208.19000001</v>
+        <v>85359803.48000002</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1236404.71</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -553,16 +553,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1236404.71</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -581,7 +581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -600,7 +600,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -619,7 +619,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -638,26 +638,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>85359803.48000002</v>
+        <v>84309803.48000002</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -667,16 +667,16 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1050000</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -695,26 +695,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>84309803.48000002</v>
+        <v>82982043.48000002</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1327760</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -724,35 +724,35 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1327760</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>82982043.48000002</v>
+        <v>75867964.53000002</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>7114078.95</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -762,16 +762,16 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7114078.95</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -790,7 +790,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -809,7 +809,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -828,26 +828,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>75867964.53000002</v>
+        <v>-153105388.2</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>228973352.73</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -857,16 +857,16 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>228973352.73</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -885,26 +885,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-153105388.2</v>
+        <v>-158105388.2</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -914,16 +914,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -942,7 +942,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -961,7 +961,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -980,7 +980,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -999,26 +999,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-158105388.2</v>
+        <v>-163105388.2</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1028,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -458,16 +458,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>36078943.3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -486,7 +486,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -505,26 +505,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86596208.19000001</v>
+        <v>85359803.48000002</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1236404.71</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -534,16 +534,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1236404.71</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -562,7 +562,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -581,7 +581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -600,7 +600,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -619,26 +619,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>85359803.48000002</v>
+        <v>84309803.48000002</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -648,16 +648,16 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1050000</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -676,26 +676,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84309803.48000002</v>
+        <v>82982043.48000002</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1327760</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -705,35 +705,35 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1327760</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>82982043.48000002</v>
+        <v>75867964.53000002</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>7114078.95</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -743,16 +743,16 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>7114078.95</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -771,7 +771,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -790,7 +790,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -809,26 +809,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>75867964.53000002</v>
+        <v>-153105388.2</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>228973352.73</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -838,16 +838,16 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>228973352.73</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -866,26 +866,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-153105388.2</v>
+        <v>-158105388.2</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -895,16 +895,16 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -923,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -942,7 +942,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -961,7 +961,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -980,26 +980,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-158105388.2</v>
+        <v>-163105388.2</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1009,16 +1009,16 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B32" t="n">

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -467,7 +467,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -486,26 +486,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86596208.19000001</v>
+        <v>85359803.48000002</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1236404.71</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -515,16 +515,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1236404.71</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -543,7 +543,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -562,7 +562,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -581,7 +581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -600,26 +600,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85359803.48000002</v>
+        <v>84309803.48000002</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -629,16 +629,16 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1050000</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -657,26 +657,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>84309803.48000002</v>
+        <v>82982043.48000002</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1327760</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -686,35 +686,35 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1327760</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>82982043.48000002</v>
+        <v>75867964.53000002</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>7114078.95</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -724,16 +724,16 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7114078.95</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -752,7 +752,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -771,7 +771,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -790,26 +790,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75867964.53000002</v>
+        <v>-153105388.2</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>228973352.73</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -819,16 +819,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>228973352.73</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -847,26 +847,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-153105388.2</v>
+        <v>-158105388.2</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -904,7 +904,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -923,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -942,7 +942,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -961,26 +961,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-158105388.2</v>
+        <v>-163105388.2</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -990,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1018,7 +1018,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B32" t="n">

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>138636841.87</v>
+        <v>23000000</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138636841.87</v>
+        <v>23000000</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138636841.87</v>
+        <v>23000000</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>138636841.87</v>
+        <v>23000000</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137586841.87</v>
+        <v>21950000</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>137586841.87</v>
+        <v>21950000</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>137586841.87</v>
+        <v>21950000</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136259081.87</v>
+        <v>20622240</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136259081.87</v>
+        <v>20622240</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129145002.92</v>
+        <v>13508161.05</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>129145002.92</v>
+        <v>13508161.05</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>129145002.92</v>
+        <v>13508161.05</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>129145002.92</v>
+        <v>13508161.05</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>129145002.92</v>
+        <v>13508161.05</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-100178349.81</v>
+        <v>-215815191.68</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-100178349.81</v>
+        <v>-215815191.68</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-100178349.81</v>
+        <v>-215815191.68</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-105178349.81</v>
+        <v>-220815191.68</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-105178349.81</v>
+        <v>-220815191.68</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-105178349.81</v>
+        <v>-220815191.68</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-105178349.81</v>
+        <v>-220815191.68</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-105178349.81</v>
+        <v>-220815191.68</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-105178349.81</v>
+        <v>-220815191.68</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-111283807.81</v>
+        <v>-226920649.68</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-111283807.81</v>
+        <v>-226920649.68</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-111283807.81</v>
+        <v>-226920649.68</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-111283807.81</v>
+        <v>-226920649.68</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-111283807.81</v>
+        <v>-226920649.68</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-111283807.81</v>
+        <v>-226920649.68</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-116283807.81</v>
+        <v>-231920649.68</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-116283807.81</v>
+        <v>-231920649.68</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -68489,7 +68489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68522,19 +68522,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>chequesDisponible</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>143290000</v>
+        <v>12000000</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>saldos.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>saldos.csv</t>
         </is>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -467,7 +467,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -486,7 +486,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -505,26 +505,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23000000</v>
+        <v>21950000</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -534,16 +534,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1050000</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -562,26 +562,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21950000</v>
+        <v>20622240</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1327760</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -591,35 +591,35 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1327760</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20622240</v>
+        <v>13508161.05</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>7114078.95</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -629,16 +629,16 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>7114078.95</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -657,7 +657,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -676,7 +676,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -695,26 +695,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13508161.05</v>
+        <v>-215815191.68</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>229323352.73</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -724,16 +724,16 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>229323352.73</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -752,26 +752,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-215815191.68</v>
+        <v>-220815191.68</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -781,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -809,7 +809,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -828,7 +828,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -847,7 +847,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -866,26 +866,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-220815191.68</v>
+        <v>-226920649.68</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>6105458</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -895,16 +895,16 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6105458</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -923,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -942,7 +942,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -961,7 +961,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -980,26 +980,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-226920649.68</v>
+        <v>-231920649.68</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1009,16 +1009,16 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B32" t="n">

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -31321,7 +31321,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -34681,7 +34681,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -34737,7 +34737,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -36529,7 +36529,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -38153,7 +38153,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -38265,7 +38265,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -38321,7 +38321,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -43137,7 +43137,7 @@
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -48457,7 +48457,7 @@
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
@@ -48513,7 +48513,7 @@
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H848" t="inlineStr">
@@ -51537,7 +51537,7 @@
       </c>
       <c r="G902" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>rechazado</t>
         </is>
       </c>
       <c r="H902" t="inlineStr">

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -467,7 +467,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -486,26 +486,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23000000</v>
+        <v>21950000</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -515,16 +515,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1050000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -543,26 +543,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21950000</v>
+        <v>20622240</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1327760</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -572,35 +572,35 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1327760</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20622240</v>
+        <v>13508161.05</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7114078.95</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -610,16 +610,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>7114078.95</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -638,7 +638,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -657,7 +657,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -676,26 +676,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13508161.05</v>
+        <v>-215815191.68</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>229323352.73</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -705,16 +705,16 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>229323352.73</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -733,26 +733,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-215815191.68</v>
+        <v>-220815191.68</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -762,16 +762,16 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -790,7 +790,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -809,7 +809,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -828,7 +828,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -847,26 +847,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-220815191.68</v>
+        <v>-226920649.68</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>6105458</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>6105458</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -904,7 +904,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -923,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -942,7 +942,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -961,26 +961,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-226920649.68</v>
+        <v>-231920649.68</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -990,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1018,20 +1018,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-231920649.68</v>
+        <v>-236920649.68</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20058152.5</v>
+        <v>6000000</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12944073.55</v>
+        <v>-1114078.95</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12944073.55</v>
+        <v>-1114078.95</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12944073.55</v>
+        <v>-1114078.95</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12944073.55</v>
+        <v>-1114078.95</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12944073.55</v>
+        <v>-1114078.95</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-219570852.09</v>
+        <v>-233629004.59</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-219570852.09</v>
+        <v>-233629004.59</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-219570852.09</v>
+        <v>-233629004.59</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-224570852.09</v>
+        <v>-238629004.59</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-224570852.09</v>
+        <v>-238629004.59</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-224570852.09</v>
+        <v>-238629004.59</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-224570852.09</v>
+        <v>-238629004.59</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-224570852.09</v>
+        <v>-238629004.59</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-224570852.09</v>
+        <v>-238629004.59</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-230676310.09</v>
+        <v>-244734462.59</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-230946901.65</v>
+        <v>-245005054.15</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-230946901.65</v>
+        <v>-245005054.15</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-230946901.65</v>
+        <v>-245005054.15</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-230946901.65</v>
+        <v>-245005054.15</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-230946901.65</v>
+        <v>-245005054.15</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-235946901.65</v>
+        <v>-250005054.15</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-235946901.65</v>
+        <v>-250005054.15</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-235946901.65</v>
+        <v>-250005054.15</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-240946901.65</v>
+        <v>-255005054.15</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-240946901.65</v>
+        <v>-255005054.15</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-240946901.65</v>
+        <v>-255005054.15</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-240946901.65</v>
+        <v>-255005054.15</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-245946901.65</v>
+        <v>-260005054.15</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-247274661.65</v>
+        <v>-261332814.15</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-247274661.65</v>
+        <v>-261332814.15</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -22009,7 +22009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22042,40 +22042,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>chequesDisponible</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12000000</v>
+        <v>6000000</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>saldos.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>principal</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
         <is>
           <t>saldos.csv</t>
         </is>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,83 +448,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13000000</v>
+        <v>-10512760.01</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>285000.01</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13000000</v>
+        <v>-24537767.27</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>14025007.26</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-10227760</v>
+        <v>-24537767.27</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>23227760</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-10512760.01</v>
+        <v>-24537767.27</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>285000.01</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -534,16 +534,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>14025007.26</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -562,7 +562,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -581,30 +581,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-24537767.27</v>
+        <v>-256630928.09</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>232093160.82</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-24537767.27</v>
+        <v>-256630928.09</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -619,11 +619,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-24537767.27</v>
+        <v>-256630928.09</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -638,74 +638,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-256630928.09</v>
+        <v>-258880928.09</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>232093160.82</v>
+        <v>2250000</v>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-256630928.09</v>
+        <v>-260280928.09</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1400000</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-256630928.09</v>
+        <v>-265280928.09</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-258880928.09</v>
+        <v>-271234003.17</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2250000</v>
+        <v>5953075.08</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -714,17 +714,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-260280928.09</v>
+        <v>-271795337.63</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1400000</v>
+        <v>561334.46</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -733,45 +733,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-265280928.09</v>
+        <v>-271795337.63</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-271234003.17</v>
+        <v>-271795337.63</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5953075.08</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -781,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>561334.46</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -809,30 +809,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-271795337.63</v>
+        <v>-276795337.63</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-271795337.63</v>
+        <v>-276795337.63</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -847,11 +847,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-271795337.63</v>
+        <v>-276795337.63</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -876,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -904,7 +904,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -923,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -942,7 +942,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -961,7 +961,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -980,7 +980,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -999,7 +999,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1018,20 +1018,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-276795337.63</v>
+        <v>-281795337.63</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,87 +448,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>140000000</v>
+        <v>-83261303.01999995</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>140000000</v>
+        <v>-89214378.09999995</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5953075.08</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>140000000</v>
+        <v>-89775712.55999994</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>561334.46</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-74611303.02000001</v>
+        <v>-89775712.55999994</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>214611303.02</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-74611303.02000001</v>
+        <v>-89775712.55999994</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -543,55 +543,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-74611303.02000001</v>
+        <v>-94873168.03999995</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5097455.48</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-76861303.02000001</v>
+        <v>-94873168.03999995</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2250000</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-78261303.02000001</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1400000</v>
+        <v>5000000</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -600,68 +600,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-83261303.02000001</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-89214378.10000001</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>5953075.08</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-89775712.56</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>561334.46</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-89775712.56</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -676,11 +676,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-89775712.56</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -695,30 +695,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-94873168.04000001</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5097455.48</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-94873168.04000001</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -733,49 +733,49 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-99873168.04000001</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-99873168.04000001</v>
+        <v>-100031434.6999999</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>158266.66</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-99873168.04000001</v>
+        <v>-100031434.6999999</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -790,30 +790,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-99873168.04000001</v>
+        <v>-105031434.6999999</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-99873168.04000001</v>
+        <v>-105031434.6999999</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -828,49 +828,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-99873168.04000001</v>
+        <v>-115767550.3599999</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>10736115.66</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-99873168.04000001</v>
+        <v>-120767550.3599999</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-99873168.04000001</v>
+        <v>-120767550.3599999</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -885,11 +885,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-99873168.04000001</v>
+        <v>-120767550.3599999</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -904,30 +904,30 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-100031434.7</v>
+        <v>-120767550.3599999</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>158266.66</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-100031434.7</v>
+        <v>-120767550.3599999</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -942,30 +942,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-105031434.7</v>
+        <v>-334894558.92</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>5000000</v>
+        <v>214127008.56</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-105031434.7</v>
+        <v>-334894558.92</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -980,30 +980,30 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-115767550.36</v>
+        <v>-334894558.92</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>10736115.66</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-120767550.36</v>
+        <v>-339894558.92</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1018,20 +1018,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-120767550.36</v>
+        <v>-343792943.2499999</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>3898384.33</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,17 +448,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-83261303.01999995</v>
+        <v>-89214378.09999995</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5000000</v>
+        <v>5953075.08</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -467,17 +467,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-89214378.09999995</v>
+        <v>-89775712.55999994</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5953075.08</v>
+        <v>561334.46</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -486,7 +486,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,16 +496,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>561334.46</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -524,26 +524,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-89775712.55999994</v>
+        <v>-94873168.03999995</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5097455.48</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -553,35 +553,35 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>5097455.48</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-94873168.03999995</v>
+        <v>-99873168.03999995</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -591,16 +591,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -619,7 +619,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -638,7 +638,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -657,7 +657,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -676,7 +676,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -695,7 +695,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -714,7 +714,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -733,26 +733,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-99873168.03999995</v>
+        <v>-100031434.6999999</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>158266.66</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -762,35 +762,35 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>158266.66</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-100031434.6999999</v>
+        <v>-105031434.6999999</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -800,45 +800,45 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-105031434.6999999</v>
+        <v>-115767550.3599999</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>10736115.66</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-115767550.3599999</v>
+        <v>-120767550.3599999</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>10736115.66</v>
+        <v>5000000</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -847,7 +847,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -857,16 +857,16 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -885,7 +885,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -904,7 +904,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -923,26 +923,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-120767550.3599999</v>
+        <v>-334894558.92</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>214127008.56</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -952,16 +952,16 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>214127008.56</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -980,45 +980,45 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-334894558.92</v>
+        <v>-339894558.92</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-339894558.92</v>
+        <v>-343792943.2499999</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>5000000</v>
+        <v>3898384.33</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1028,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3898384.33</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -458,16 +458,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -486,26 +486,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-5000000</v>
+        <v>-6152855</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1152855</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -515,16 +515,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1152855</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -543,7 +543,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -562,7 +562,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -581,7 +581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -600,26 +600,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-6152855</v>
+        <v>-6311121.66</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>158266.66</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -629,35 +629,35 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>158266.66</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-6311121.66</v>
+        <v>-11311121.66</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -667,45 +667,45 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-11311121.66</v>
+        <v>-22047237.32</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>10736115.66</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-22047237.32</v>
+        <v>-27047237.32</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>10736115.66</v>
+        <v>5000000</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -724,16 +724,16 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -752,7 +752,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -771,7 +771,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -790,26 +790,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-27047237.32</v>
+        <v>-260552558.9</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>233505321.58</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -819,16 +819,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>233505321.58</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -847,74 +847,74 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-260552558.9</v>
+        <v>-265552558.9</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-265552558.9</v>
+        <v>-269450943.23</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5000000</v>
+        <v>3898384.33</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-269450943.23</v>
+        <v>-270825943.23</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>3898384.33</v>
+        <v>1375000</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-270825943.23</v>
+        <v>-271978798.23</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1375000</v>
+        <v>1152855</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -933,16 +933,16 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1152855</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -961,7 +961,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -980,7 +980,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -999,26 +999,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-271978798.23</v>
+        <v>-277540132.71</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>5561334.48</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1028,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>5561334.48</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-49502243.38</v>
+        <v>-55244595.77</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-72843830.52</v>
+        <v>-78586182.91</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-77843830.52</v>
+        <v>-83586182.91</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-77843830.52</v>
+        <v>-83586182.91</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-77843830.52</v>
+        <v>-83586182.91</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-77843830.52</v>
+        <v>-83586182.91</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-77843830.52</v>
+        <v>-83586182.91</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-311349152.1</v>
+        <v>-317091504.49</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-311349152.1</v>
+        <v>-317091504.49</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-311349152.1</v>
+        <v>-317091504.49</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-316349152.1</v>
+        <v>-322091504.49</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-320247536.43</v>
+        <v>-325989888.82</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-321622536.43</v>
+        <v>-327364888.82</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-322775391.43</v>
+        <v>-328517743.82</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-322775391.43</v>
+        <v>-328517743.82</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-322775391.43</v>
+        <v>-328517743.82</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-322775391.43</v>
+        <v>-328517743.82</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-322775391.43</v>
+        <v>-328517743.82</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-328336725.91</v>
+        <v>-334079078.3</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-328336725.91</v>
+        <v>-334079078.3</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-328336725.91</v>
+        <v>-334079078.3</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-328336725.91</v>
+        <v>-334079078.3</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-328336725.91</v>
+        <v>-334079078.3</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-333336725.91</v>
+        <v>-339079078.3</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-333336725.91</v>
+        <v>-339079078.3</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-336586165.87</v>
+        <v>-342328518.26</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-336586165.87</v>
+        <v>-342328518.26</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-339618424.93</v>
+        <v>-345360777.32</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-339618424.93</v>
+        <v>-345360777.32</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-339618424.93</v>
+        <v>-345360777.32</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-344618424.93</v>
+        <v>-350360777.32</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18469,7 +18469,11 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Base cero - ver saldo real en Galicia</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>saldos.csv</t>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,45 +448,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-55244595.77</v>
+        <v>-78586182.91</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>44343976.72</v>
+        <v>23341587.14</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-78586182.91</v>
+        <v>-83586182.91</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>23341587.14</v>
+        <v>5000000</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,16 +496,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -524,7 +524,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -543,7 +543,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -562,26 +562,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-83586182.91</v>
+        <v>-317091504.49</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>233505321.58</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -591,16 +591,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>233505321.58</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -619,74 +619,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-317091504.49</v>
+        <v>-322091504.49</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-322091504.49</v>
+        <v>-325989888.82</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>5000000</v>
+        <v>3898384.33</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-325989888.82</v>
+        <v>-327364888.82</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3898384.33</v>
+        <v>1375000</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-327364888.82</v>
+        <v>-328517743.82</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1375000</v>
+        <v>1152855</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -695,7 +695,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -705,16 +705,16 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1152855</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -733,7 +733,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -752,7 +752,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -771,26 +771,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-328517743.82</v>
+        <v>-334079078.3</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>5561334.48</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -800,16 +800,16 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5561334.48</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -828,7 +828,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -847,7 +847,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -866,26 +866,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-334079078.3</v>
+        <v>-339079078.3</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -895,35 +895,35 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-339079078.3</v>
+        <v>-342328518.26</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3249439.96</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -933,35 +933,35 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3249439.96</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-342328518.26</v>
+        <v>-345360777.32</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>3032259.06</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -971,16 +971,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>3032259.06</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -999,26 +999,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-345360777.32</v>
+        <v>-350360777.32</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1028,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,26 +448,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-78586182.91</v>
+        <v>-83586182.91</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>23341587.14</v>
+        <v>5000000</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -477,16 +477,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -505,7 +505,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -524,7 +524,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -543,26 +543,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-83586182.91</v>
+        <v>-317091504.49</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>233505321.58</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -572,16 +572,16 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>233505321.58</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -600,74 +600,74 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-317091504.49</v>
+        <v>-322091504.49</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-322091504.49</v>
+        <v>-325989888.82</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>5000000</v>
+        <v>3898384.33</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-325989888.82</v>
+        <v>-327364888.82</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3898384.33</v>
+        <v>1375000</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-327364888.82</v>
+        <v>-328517743.82</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1375000</v>
+        <v>1152855</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -676,7 +676,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -686,16 +686,16 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1152855</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -714,7 +714,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -733,7 +733,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -752,26 +752,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-328517743.82</v>
+        <v>-334079078.3</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>5561334.48</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -781,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5561334.48</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -809,7 +809,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -828,7 +828,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -847,26 +847,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-334079078.3</v>
+        <v>-339079078.3</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -876,35 +876,35 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-339079078.3</v>
+        <v>-342328518.26</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>3249439.96</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -914,35 +914,35 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3249439.96</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-342328518.26</v>
+        <v>-345360777.32</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>3032259.06</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -952,16 +952,16 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>3032259.06</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -980,26 +980,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-345360777.32</v>
+        <v>-350360777.32</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1009,29 +1009,29 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-350360777.32</v>
+        <v>-373702364.48</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>23341587.16</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/flujo_bancario/TABLERO_Resumen.xlsx
+++ b/flujo_bancario/TABLERO_Resumen.xlsx
@@ -448,55 +448,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-222422117.42</v>
+        <v>-227422117.42</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-222422117.42</v>
+        <v>-231320501.7500001</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3898384.33</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-227422117.42</v>
+        <v>-232695501.7500001</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5000000</v>
+        <v>1375000</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -505,45 +505,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-231320501.7500001</v>
+        <v>-233848356.7500001</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3898384.33</v>
+        <v>1152855</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-232695501.7500001</v>
+        <v>-233848356.7500001</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1375000</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -553,16 +553,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1152855</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -581,64 +581,64 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-233848356.7500001</v>
+        <v>-241526192.8500001</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7677836.1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-233848356.7500001</v>
+        <v>-247087527.33</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5561334.48</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-241526192.8500001</v>
+        <v>-247087527.33</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>7677836.1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -648,16 +648,16 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>5561334.48</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -676,7 +676,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -695,30 +695,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-247087527.33</v>
+        <v>-252087527.33</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-247087527.33</v>
+        <v>-252087527.33</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -733,17 +733,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-252087527.33</v>
+        <v>-255336967.2900001</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5000000</v>
+        <v>3249439.96</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -752,11 +752,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-252087527.33</v>
+        <v>-255336967.2900001</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -771,30 +771,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-255336967.2900001</v>
+        <v>-258619226.3500001</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3249439.96</v>
+        <v>3282259.06</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-255336967.2900001</v>
+        <v>-258619226.3500001</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -809,7 +809,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -819,39 +819,39 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3282259.06</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-258619226.3500001</v>
+        <v>-263619226.3500001</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-258619226.3500001</v>
+        <v>-263619226.3500001</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -866,74 +866,74 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-263619226.3500001</v>
+        <v>-287830293.5000001</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5000000</v>
+        <v>24211067.15</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-263619226.3500001</v>
+        <v>-288640293.5000001</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>810000</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-287830293.5000001</v>
+        <v>-288640293.5000001</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>24211067.15</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-288640293.5000001</v>
+        <v>-293640293.5000001</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>810000</v>
+        <v>5000000</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -942,11 +942,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-288640293.5000001</v>
+        <v>-293640293.5000001</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -961,30 +961,30 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-293640293.5000001</v>
+        <v>-453516985.8600001</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>5000000</v>
+        <v>159876692.36</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-293640293.5000001</v>
+        <v>-453516985.8600001</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -999,39 +999,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-453516985.8600001</v>
+        <v>-458616985.8600001</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>159876692.36</v>
+        <v>5100000</v>
       </c>
       <c r="E31" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-453516985.8600001</v>
+        <v>-464756985.8600001</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>6140000</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
